--- a/artfynd/A 5481-2022 artfynd.xlsx
+++ b/artfynd/A 5481-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5481-2022 artfynd.xlsx
+++ b/artfynd/A 5481-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>947648</v>
       </c>
       <c r="B2" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434635.4740129218</v>
+        <v>434635</v>
       </c>
       <c r="R2" t="n">
-        <v>6478344.539110129</v>
+        <v>6478345</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2010-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,42 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97876608</v>
+        <v>98170778</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,14 +829,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra  Ryd N om (5), Vg</t>
+          <t>Ryd, N Nyckelpigevägen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434514.6290275619</v>
+        <v>434515</v>
       </c>
       <c r="R3" t="n">
-        <v>6478143.923460837</v>
+        <v>6478144</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,34 +861,14 @@
           <t>Ryd</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>OV-Skö-0260</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>barrblsndskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +884,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Enar Sahlin</t>
+          <t>Tore Mattsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -932,62 +892,61 @@
           <t>Tore Mattsson, Olle Molander</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98170930</v>
+        <v>97876608</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ryd, N Nyckelpigevägen, Vg</t>
+          <t>Södra  Ryd N om (5), Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434555.8556390709</v>
+        <v>434515</v>
       </c>
       <c r="R4" t="n">
-        <v>6478225.441028237</v>
+        <v>6478144</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,24 +971,24 @@
           <t>Ryd</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>OV-Skö-0260</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>barrblsndskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,7 +1004,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tore Mattsson</t>
+          <t>Enar Sahlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1053,19 +1012,18 @@
           <t>Tore Mattsson, Olle Molander</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98170778</v>
+        <v>98170919</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,33 +1031,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1109,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434514.6290275619</v>
+        <v>434532</v>
       </c>
       <c r="R5" t="n">
-        <v>6478143.923460837</v>
+        <v>6478132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,19 +1092,9 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,15 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98170919</v>
+        <v>98170921</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434531.7430106818</v>
+        <v>434541</v>
       </c>
       <c r="R6" t="n">
-        <v>6478132.118651696</v>
+        <v>6478107</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,19 +1194,9 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,15 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103552391</v>
+        <v>98170930</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,29 +1252,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rydskogen, Vg</t>
+          <t>Ryd, N Nyckelpigevägen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434559.6312692033</v>
+        <v>434556</v>
       </c>
       <c r="R7" t="n">
-        <v>6478231.66120328</v>
+        <v>6478226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,22 +1293,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,6 +1323,218 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98171026</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ryd, N Nyckelpigevägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>434578</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6478158</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103552391</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rydskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>434560</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6478231</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5481-2022 artfynd.xlsx
+++ b/artfynd/A 5481-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/947648</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98170778</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97876608</t>
         </is>
       </c>
     </row>
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98170919</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98170921</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98170930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98171026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,8 +1575,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103552391</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>